--- a/AAII_Financials/Quarterly/SIEGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SIEGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
   <si>
     <t>SIEGY</t>
   </si>
@@ -656,149 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -841,86 +844,89 @@
       <c r="P8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="3">
         <v>20014300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22232200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19441100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>18488400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17899200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18786500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17017900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14970000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14363700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15377500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14158900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>15563500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15440400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20059200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16749600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17039900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16298200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>25039500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>22479400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>22598000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>22241200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>24927300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>23896100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>23634700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>22552400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>25768700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -963,86 +969,89 @@
       <c r="P9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3">
         <v>12298800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13942100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12663300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12259400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11166800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11993400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10805400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9622100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8933000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10048900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8971600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9903300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9809600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12496100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>10675800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>10582800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10438000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17823500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>15801300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>15522700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>15554100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>17849700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>17030700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>15969700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>15409800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>18465200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1085,86 +1094,89 @@
       <c r="P10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R10" s="3">
         <v>7715500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8290000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6777800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6229000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6732400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6793100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6212600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5348000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5430700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5328600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5187300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5660200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5630800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7563100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6073800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6457100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5860200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7216000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6678000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7075300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6687100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7077500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6865500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7665000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>7142600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>7303400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1251,86 +1264,89 @@
       <c r="P12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3">
         <v>1583900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1708600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1523300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1474500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1357300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1557200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1290800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1151500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1086100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1244400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1185800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1308600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1269100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1572900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1359900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1367300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1299100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1735600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1506500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1565200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1373300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1656100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1511300</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1425000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1322900</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1551800</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1564,8 +1583,8 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>10</v>
+      <c r="AN14" s="3">
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>10</v>
@@ -1573,8 +1592,11 @@
       <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1617,8 +1639,8 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,8 +1761,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1780,86 +1806,89 @@
       <c r="P17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" s="3">
         <v>17548800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18318900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16795900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17111500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15767200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17038700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15260600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13466400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12588500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13975300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12931600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14183800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14117100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17557800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>15177900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>14926200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>14927400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>23528700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>20824700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>20680500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>20439300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>23346400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>22102100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>20967800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>19862000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>23667500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1902,86 +1931,89 @@
       <c r="P18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="3">
         <v>2465500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3913200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2645200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1376900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2132000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1747800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1757300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1503600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1775200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1402200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1227300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1379800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1323300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2501400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1571700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2113700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1370800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1510800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1654700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1917500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1801900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1580900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1794100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2666900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2690400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2101100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,86 +2101,89 @@
       <c r="P20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3">
         <v>302400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>459300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3463400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>725900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>702000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>424300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>194700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>689000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>399100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>209700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>480000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>427900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>479900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>407900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>564600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>553800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>350000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>435900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1373300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1141100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>478000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>518400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>154900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>759500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2190,86 +2226,89 @@
       <c r="P21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3">
         <v>3722600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5334300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>138200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3157400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3723700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3044400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2860800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2903200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2899100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2535600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2549500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2287600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3011300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4091500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2988100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3678300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2916300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2874200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2982200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4229900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3902300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3202200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3279600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3607100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>4225700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3242100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,86 +2351,89 @@
       <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3">
         <v>305700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>191300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>174100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>202900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>179000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>190600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>144900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>167400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>169500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>147400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>237800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>353400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>159200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>308700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>276500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>312200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>259600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>301300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>299800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>298400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>311900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>310800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>322000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>284100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>286400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>291100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2434,86 +2476,89 @@
       <c r="P23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3">
         <v>2462200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4181200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-992300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1899800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2655000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1981500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1807100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2025300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2004900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1464500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1469500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1454300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1644000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2600700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1695200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2366100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1665100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1559500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1790800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2992300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2631100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1748100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1990400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2537800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3163400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2080000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2556,86 +2601,89 @@
       <c r="P24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R24" s="3">
         <v>641300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1029900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>664800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>587000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>690100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>616000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>351300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>478800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>498200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>387100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>446200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>334200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>302600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>916300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>448200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>311000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>461700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>828500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>512800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>774200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>655200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>379200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>392700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>860400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>853400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>693700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,8 +2804,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2800,86 +2851,89 @@
       <c r="P26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="3">
         <v>1820900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3151300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1657200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1312900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1964900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1365500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1455800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1546500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1506700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1077300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1023300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1120100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1341400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1684400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1247000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2055100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1203400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>731000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1278100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2218200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1975800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1368800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1597700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1677400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2310100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1386300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2922,86 +2976,89 @@
       <c r="P27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R27" s="3">
         <v>1644800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2921100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1793200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1117600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1798900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1192100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1319300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1419900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1382200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>952800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1027600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1069300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1333500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1499400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1122300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1916300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1079000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>594800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1163900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2144100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1952300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1350900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1539400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1636300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2271300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1359300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3166,86 +3226,89 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3">
         <v>-8900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-2200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-7600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>4300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-16300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>64600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>111100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>892200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>23500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>871800</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-439600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-333100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-111800</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>115100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>91800</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>245200</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>135200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>24400</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>50500</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>47100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>503800</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>34800</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-16800</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>29300</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>14100</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,86 +3601,89 @@
       <c r="P32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="3">
         <v>-302400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-459300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3463400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-725900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-702000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-424300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-194700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-689000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-399100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-209700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-480000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-427900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-479900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-407900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-564600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-553800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-350000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-435900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1373300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1141100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-478000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-518400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-154900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-759500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-270000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3654,86 +3726,89 @@
       <c r="P33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R33" s="3">
         <v>1635900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2919000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1800800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1121900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1782700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1256700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1430400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2312100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1405600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1824600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>588000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>736200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1221700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1614500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1214000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2161500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1214100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>619100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1214400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2191200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2456000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1385700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1522500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1665600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2285400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1352200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,8 +3929,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3898,213 +3976,219 @@
       <c r="P35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R35" s="3">
         <v>1635900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2919000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1800800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1121900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1782700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1256700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1430400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2312100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1405600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1824600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>588000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>736200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1221700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1614500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1214000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2161500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1214100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>619100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1214400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2191200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2456000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1385700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1522500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1665600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2285400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1352200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,130 +4276,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12487100</v>
+      </c>
+      <c r="E41" s="3">
         <v>9989600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17920600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17006900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17194400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13711600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14417600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10211900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8312400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8323400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11903400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10673200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10700900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9980400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11225500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11309500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10986500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10302100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13235900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10279000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11297300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>24130700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14307500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>14573200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13182600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8843100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12815300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15178900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9437100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10628200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14819700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12256700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7784800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10749800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>11215400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>9396700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>9520100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>11598400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>11182900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>12447100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4325,11 +4414,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1201500</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -4337,11 +4426,11 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1182200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -4349,948 +4438,972 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>1108200</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>10925400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10478500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>10491500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9334300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>9538200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>8599000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7927600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>9334200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>8584900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8699700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9240000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>11103600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>11233400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>13069400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>11464000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>11729900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>11299300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>11865700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>10144400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>10626400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>10132700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>9992400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>9755700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>10085400</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>10037200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>9499600</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46237900</v>
+      </c>
+      <c r="E43" s="3">
         <v>47513000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46091300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41251900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>44966500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41999600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40229800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38675000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28737800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28660000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28937800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35919800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27941000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>27284900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27925900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27765300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>26989200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>26188600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>25943400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>25800400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>24573100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>21962500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>21282700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>21943300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>22461800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>24030600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>33874100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>37124500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>35800200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>34793900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>34533100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>31430400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>29901800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>28899100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>29119000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>29882000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>20761300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>20843300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>20116800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>20045200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13571300</v>
+      </c>
+      <c r="E44" s="3">
         <v>13258400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13032800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12415800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13112200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12427600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12120300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12182700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12970100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13377900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13467400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12222700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13057900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12581500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12450500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11483500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>11736200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10973700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>10564600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>9515500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>9475400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8121500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7904100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8090400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>9481100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>9569100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>18004600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18137200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18655400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18701400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>17891600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>15379000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>16156000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>16172400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>16158900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>15578800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>23339600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>23185100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>22082900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>21316400</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2125000</v>
+      </c>
+      <c r="E45" s="3">
         <v>8743200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2692300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4049000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1991800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2063300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4329600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6176700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15844900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14036000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13335900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4258000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13379900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12883500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2369200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2539600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3166400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3581600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1873800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2124700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1755200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1571000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3165500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1668900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>47403300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>48519700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2511100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2692500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2531600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2367300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2349300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1993700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2067500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2175500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1936600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4957000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2066700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1916800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1676200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1637500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74421300</v>
+      </c>
+      <c r="E46" s="3">
         <v>79504200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>79737000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75925100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>77264800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>70202100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>71097400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>68428500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>65865200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>64397500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>67644500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>64181800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>65079700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>62730300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>64896500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>63576500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>63369900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>60380300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>61156000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>56319700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>55028700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>65119900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>55244700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>54975500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>101768800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>102066100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>78438600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>86202500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>77888300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>78220700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>80893000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>71502200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>66054600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>68623200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>68562600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>68160900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>65443400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>67629100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>65096000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>64945700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1116200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1061900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1014400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12909800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1087500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1085200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1097400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7683500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1136800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1275200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1281100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4629600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3506600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5304200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29823200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>33348200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>31633200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>33371300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>32653100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>32848700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>31746300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>28604900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>28956000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>31794000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>24796400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>25346000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>24782600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>27056400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>25019700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>25335500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>24967100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22543000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>22100500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>21630800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>23888300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>24426800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>25769900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>27684300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>27944900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>27727700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15756900</v>
+      </c>
+      <c r="E48" s="3">
         <v>15524000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15568900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15088600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14852600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14004500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13287100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13470900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12878000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13069400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13121500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12463000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12507600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12410900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12626600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12679900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12419600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12105300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12156300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11870700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11237000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10298900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9989500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10638500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11245100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11644400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16910500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14924100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13879200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14074500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13777800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12605600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12157100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12203900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12181400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12316100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12254400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12244000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12059700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>11922400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>60896800</v>
+      </c>
+      <c r="E49" s="3">
         <v>61364000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>61731800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>62031000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>56950100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>55419400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>44336900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>45702700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>45044500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>45627400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>46503800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45369400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>46170300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>46169100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>48045500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>49773800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>46663200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>45317200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>45112100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>43613400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>41785700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>25794600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24965700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>26245400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>28500000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>30084900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>46092100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>48950600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>46096100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>47582400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>46788200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>42614900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>42278500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>42292300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>43301000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>43569100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>44476800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>42453200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>38471600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>37445700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37628200</v>
+      </c>
+      <c r="E52" s="3">
         <v>34378000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39911900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4616900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>37873200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32482700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30757800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4968800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31022200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29029000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28701200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3874900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26747800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26612300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4023900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4349800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4763700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5007300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5606200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5438300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4969400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4578300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4802900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4939400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5056400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4936400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5787800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6918700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5967900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5757300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5357800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4596500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4630300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4895200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4720200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4242200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>3778900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4188200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4597800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>5526300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>191410900</v>
+      </c>
+      <c r="E54" s="3">
         <v>193671200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>199758100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>195004100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>190786800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>175738200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>163427900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>164858400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>158706700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>156166800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>160035400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>153546800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>156860300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>155364000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>159415800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>163728200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>158849500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>156181400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>156683800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>150089700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>144767200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>134396500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>123958800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>128592700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>171366700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>174077900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>172011600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>184052300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>168851000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>170970500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>171783900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>153862300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>147220900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>149645400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>152653500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>152715200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>151723300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>154198700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>148170000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>147567900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10627200</v>
+      </c>
+      <c r="E57" s="3">
         <v>10319400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10064600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10774400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10068100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9472500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9008200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9862800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8944600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9652600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10173500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10721800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10321000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10369400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10459100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11149600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9932200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9691200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9207300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9511200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8500000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7425300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7171100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8171400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6688400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7001500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11821700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13975900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12247500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12271800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11978700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11869000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10496900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10028300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9988000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>10946100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>10770000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9352900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>8818800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>9446800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9825200</v>
+      </c>
+      <c r="E58" s="3">
         <v>14571700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16003300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13110400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12028200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20414000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8436700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7358900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8367100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7697700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10733900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7920200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10575300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10224900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7870600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7195300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10771100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11391400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10525600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>16844900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>11403100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8705400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7694800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6810700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5955300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7799800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7622600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7391600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>11469900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>10756200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9369800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5601100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3361000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>6353800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6216900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6111500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>7700200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>6085000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5627200</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>7284700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>31087600</v>
+      </c>
+      <c r="E59" s="3">
         <v>32201100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31872700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23573900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29540800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28948300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28823900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24433400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>29613200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28393600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>30394600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21709400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28031700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26151700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27396500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27785900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27075200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>25229500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24419000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>25142400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22638000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>19218600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>20481300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>20427900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>49656000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>49887000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>37285100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>40767700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>38105900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>37718600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>39414800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>35555100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>34141200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>34551700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>35443700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>34640300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>32000300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>33477100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>33731800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>33643700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51540000</v>
+      </c>
+      <c r="E60" s="3">
         <v>57092100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>57940600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55451100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51637100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>58834800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46268800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>48977200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46924900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45743900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51302100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47537000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48927900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>46746000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>45726200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>46130800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47778500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>46312100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>44151900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43076000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>42541100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>35349300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>35347200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>35410000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>62299700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>64688400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>56729400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>62135200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>61823300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>60746600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>60763400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>53025200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>47999100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>50933900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>51648600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>51697900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>50470500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>48915000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>48177900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>50375200</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>47211200</v>
+      </c>
+      <c r="E61" s="3">
         <v>47876200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>50293500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52611800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54546100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>41758500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43208400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>46086300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>45101300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>46732100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43782500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>41398200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42798000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>44131900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46670900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>47527000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>45327000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>44760600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>45316100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>44022600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>42672300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>44476300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>36689600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>39445400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>44311700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>41581400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37631800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37256800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>30732300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>32870400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>33201700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>30038100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28666600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>28340300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>29600300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>30043500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>32026100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>38674700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>31563800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>30405200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4507000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4442500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4506300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4383400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4414600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4227200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4238500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4407800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4722000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4933600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5153100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5199000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5827500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5751800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10287400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10842700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10029000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10184900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10689400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10232700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>10170600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9048400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>10673500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12405000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>14187300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>14498800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18940700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>22205400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>20458800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>20995700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>20836600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17583200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>17860100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>18649700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>20484200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>20910500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>20396700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>21366900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>22391600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>25920100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>105545500</v>
+      </c>
+      <c r="E66" s="3">
         <v>111881700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>115197800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>114784700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>113230800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>107455700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>96302900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>102142500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100025700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100901900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103844400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>97395200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>101752200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>100611700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>108788500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>110887400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>109098300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>106774900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>105685500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>102533800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>100251800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>93435900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>86123900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>90823500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>123537900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>123689500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>116414700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>125098400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>116177700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>117771900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>117952500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>103496400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>97249900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>100645900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>103254500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>104266500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>104659200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>109687800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>102846900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>107410700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60546100</v>
+      </c>
+      <c r="E72" s="3">
         <v>53826800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>61377200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58196600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55429200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>45620400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>44634000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>44230400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40392200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38108700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40390200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>39019900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38279500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>37559800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43769000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42103000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40594800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42539600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>44878900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>42652800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>40561600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>37045900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35373800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>34331700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>43341900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>44554300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>48555800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>51226600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>47708900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>47185300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>48717600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>45427100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>44466800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>44000000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>42359600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>40160500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>38469700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>35296500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>36673300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>32225800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77984700</v>
+      </c>
+      <c r="E76" s="3">
         <v>74238400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>76882700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>73030600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>71153300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>62228700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>61500200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>57176000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>53360100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49842500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>50857700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>50573700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>49521800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49103700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>50627300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>52840800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49751200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49406600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>50998300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47555900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>44515400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>40960600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>37834900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>37769200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>47828800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>50388300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>55596900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>58953900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52673300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53198600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>53831400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>50365900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>49971100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>48999500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>49399000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>48448700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>47064100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>44510900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>45323200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>40157200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,135 +8659,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8642,86 +8836,89 @@
       <c r="P81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R81" s="3">
         <v>1635900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2919000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1800800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1121900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1782700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1256700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1430400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2312100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1405600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1824600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>588000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>736200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1221700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1614500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1214000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2161500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1214100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>619100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1214400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2191200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2456000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1385700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1522500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1665600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2285400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1352200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>798600</v>
+      </c>
+      <c r="E83" s="3">
         <v>676600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>623300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>449500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>638600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>664600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>626700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>201100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>636500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>910500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>649800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>367700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>649200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>789800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>954800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>961800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>956400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1054600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>889700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>872300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>908800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>710500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>724800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>923700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>842200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>479900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1208100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1182100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1016400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1000000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>991600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1013500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>891600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>939100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>959300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1143300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>967200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>785300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>775900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>871000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5465600</v>
+      </c>
+      <c r="E89" s="3">
         <v>2583900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1374900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7208700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4077500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1679600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2160700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6361800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2849000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1988300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1612700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5706000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3764200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3128000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>577100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4494600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3001000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1993100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1612300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4735100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2850300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1627200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1338300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-21800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3294500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>756500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>599600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7463900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1281100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1299100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>224900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4696200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1625000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1495600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1540500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3636400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1781700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1423800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1331100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>5149500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-726600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-605300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-580000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-980900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-650600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-594500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-521800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-756200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-557200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-526500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-445500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-766300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-521800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-551900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-436000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-708000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-471000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-513000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-392000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-620000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-442200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-370600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-335800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-539700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-373100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-231500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-549900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1016700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-770500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-717700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-628000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1058900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-662100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-607000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-563200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-969400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-724800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1115100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-988300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-959000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-701500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-386300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-495500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6921300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1468000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7364900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2742500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1511300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-486400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1069200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-532800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1318800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-619000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-789900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-704400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-462500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-145800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1017700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1074200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1740300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15342100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1093300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-457300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1363800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-290200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1588600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2480600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1974700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1202300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1320600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1522800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2462200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1002500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1308200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>592400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1884900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1668400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-4665900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-369800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2619900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,53 +10426,54 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3">
         <v>4802300</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3">
         <v>4423900</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3">
         <v>4001500</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q96" s="3">
         <v>3652800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2254100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9908900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-23500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-318000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>219600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4490900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-445200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3039300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2202900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4218400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-208900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4145900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2193200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3295300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>252500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3821400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2412300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4005800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2108200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4380800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1165900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6710700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-631900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1268300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2092400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-758800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>794900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-262100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-890500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4363700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2801500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2307100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3425800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-639500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-380400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1729000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1276800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>3617700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2304200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>2442700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-534400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-144800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>260900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-164000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>20400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>11900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-113800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>56100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-279500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-72800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-482000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>129400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>236300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>117800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-499500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>142700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>245900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>115000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>233300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>165800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-55000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>324600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-220500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-293700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-80200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-89200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>126200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-203500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>192600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>78900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-137300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>68100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-13500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>50500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-130200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-402800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>39900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>63400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2577400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7596000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>893500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-161900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2294800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1339200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4718900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1647300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>180000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3287300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>757200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>297400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>672500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1030000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-374400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>353400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>688800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2915400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2879600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1220100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13712700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9755800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>28600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-411000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4996400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1671100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1175400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5353200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1015200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4192700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1582600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4403800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2735100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-465600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1803000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-107700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1566300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>415500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1279500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>4972300</v>
       </c>
     </row>
